--- a/samples/미수금_샘플.xlsx
+++ b/samples/미수금_샘플.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,11 @@
           <t>입금계좌</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>카톡이름</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,6 +518,11 @@
           <t>국민 123456-01-234567 (도로시브루)</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>하늘카페 이사장님</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,6 +565,11 @@
           <t>국민 123456-01-234567 (도로시브루)</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>하늘카페 이사장님</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +612,11 @@
           <t>국민 123456-01-234567 (도로시브루)</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>하늘카페 이사장님</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -639,6 +659,7 @@
           <t>국민 123456-01-234567 (도로시브루)</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -681,6 +702,7 @@
           <t>국민 123456-01-234567 (도로시브루)</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -723,6 +745,7 @@
           <t>국민 123456-01-234567 (도로시브루)</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/미수금_샘플.xlsx
+++ b/samples/미수금_샘플.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
           <t>카톡이름</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>채팅방</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,6 +528,7 @@
           <t>하늘카페 이사장님</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -570,6 +576,7 @@
           <t>하늘카페 이사장님</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -617,6 +624,7 @@
           <t>하늘카페 이사장님</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -660,6 +668,11 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>베이커리온 납품방</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -703,6 +716,7 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -746,6 +760,7 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/미수금_샘플.xlsx
+++ b/samples/미수금_샘플.xlsx
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>카페하늘</t>
+          <t>마닐라푸드</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,34 +498,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>원두 에티오피아 5kg</t>
+          <t>해상운임 인천→마닐라 2CBM</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>180000</v>
+        <v>380000</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>180000</v>
+        <v>380000</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>46275</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>김도로시 010-0000-1111</t>
+          <t>KF로지스틱 김담당 010-0000-1111</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>국민 123456-01-234567 (도로시브루)</t>
+          <t>국민 123456-01-234567 (KF로지스틱)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>하늘카페 이사장님</t>
+          <t>마닐라푸드 이사장님</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>카페하늘</t>
+          <t>마닐라푸드</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,34 +546,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>원두 콜롬비아 3kg</t>
+          <t>냉동창고 보관료(8월)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105000</v>
+        <v>150000</v>
       </c>
       <c r="F3" t="n">
         <v>50000</v>
       </c>
       <c r="G3" t="n">
-        <v>55000</v>
+        <v>100000</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>46290</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>김도로시 010-0000-1111</t>
+          <t>KF로지스틱 김담당 010-0000-1111</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>국민 123456-01-234567 (도로시브루)</t>
+          <t>국민 123456-01-234567 (KF로지스틱)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>하늘카페 이사장님</t>
+          <t>마닐라푸드 이사장님</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>카페하늘</t>
+          <t>마닐라푸드</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>드립백 200개</t>
+          <t>통관 수수료</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -611,17 +611,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>김도로시 010-0000-1111</t>
+          <t>KF로지스틱 김담당 010-0000-1111</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>국민 123456-01-234567 (도로시브루)</t>
+          <t>국민 123456-01-234567 (KF로지스틱)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>하늘카페 이사장님</t>
+          <t>마닐라푸드 이사장님</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -629,7 +629,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>베이커리온</t>
+          <t>세부마트</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>블렌드 원두 10kg</t>
+          <t>해상운임 인천→세부 냉동 1CBM</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -659,25 +659,25 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>박브루 010-0000-2222</t>
+          <t>KF로지스틱 박담당 010-0000-2222</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>국민 123456-01-234567 (도로시브루)</t>
+          <t>국민 123456-01-234567 (KF로지스틱)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>베이커리온 납품방</t>
+          <t>KF - 세부마트 [CEBU]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>오피스커피</t>
+          <t>클락정육</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>콜드브루 원액 20L</t>
+          <t>내륙운송비 마닐라→클락</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -707,12 +707,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>김도로시 010-0000-1111</t>
+          <t>KF로지스틱 김담당 010-0000-1111</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>국민 123456-01-234567 (도로시브루)</t>
+          <t>국민 123456-01-234567 (KF로지스틱)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -721,7 +721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스튜디오카페</t>
+          <t>보홀상회</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>원두 디카페인 2kg</t>
+          <t>냉동창고 보관료(9월)</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -751,12 +751,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>박브루 010-0000-2222</t>
+          <t>KF로지스틱 박담당 010-0000-2222</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>국민 123456-01-234567 (도로시브루)</t>
+          <t>국민 123456-01-234567 (KF로지스틱)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
